--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486793_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486793_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.651199999999999</v>
+        <v>7.2775</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9744</v>
+        <v>4.1471</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6768</v>
+        <v>3.1305</v>
       </c>
       <c r="G2" t="n">
         <v>4.7846</v>
@@ -610,13 +610,13 @@
         <v>1.3515</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7048</v>
+        <v>0.3312</v>
       </c>
       <c r="T2" t="n">
-        <v>0.965</v>
+        <v>0.1377</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7398</v>
+        <v>0.1935</v>
       </c>
       <c r="V2" t="n">
         <v>2.741</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. DEL CERRO RUIZ</t>
+          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2634</v>
+        <v>4.1265</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5339</v>
+        <v>0.1267</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7296</v>
+        <v>3.9999</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0524</v>
+        <v>2.8133</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5175</v>
+        <v>1.8615</v>
       </c>
       <c r="I3" t="n">
-        <v>1.535</v>
+        <v>0.9517</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2816</v>
+        <v>3.07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2771</v>
+        <v>3.1038</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0046</v>
+        <v>-0.0338</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7708</v>
+        <v>-0.2567</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-1.2423</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5304</v>
+        <v>0.9856</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7377</v>
+        <v>1.1585</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7031</v>
+        <v>3.0892</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8442</v>
+        <v>-0.1308</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3028</v>
+        <v>-0.6417</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5413</v>
+        <v>0.5109</v>
       </c>
       <c r="V3" t="n">
+        <v>0.2856</v>
+      </c>
+      <c r="W3" t="n">
         <v>-0.3709</v>
       </c>
-      <c r="W3" t="n">
-        <v>-0.0852</v>
-      </c>
       <c r="X3" t="n">
-        <v>-0.2856</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
+          <t>D. DEL CERRO RUIZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0205</v>
+        <v>3.84</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5008</v>
+        <v>0.334</v>
       </c>
       <c r="F4" t="n">
-        <v>4.5213</v>
+        <v>3.5061</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8133</v>
+        <v>2.0524</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8615</v>
+        <v>0.5175</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9517</v>
+        <v>1.535</v>
       </c>
       <c r="J4" t="n">
-        <v>3.07</v>
+        <v>1.2816</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1038</v>
+        <v>1.2771</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0338</v>
+        <v>0.0046</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2567</v>
+        <v>0.7708</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2423</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9856</v>
+        <v>1.5304</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1585</v>
+        <v>1.7377</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R4" t="n">
-        <v>3.0892</v>
+        <v>2.7031</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2368</v>
+        <v>0.4208</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2692</v>
+        <v>0.1029</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0324</v>
+        <v>0.3178</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2856</v>
+        <v>-0.3709</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3709</v>
+        <v>-0.0852</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6565</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1233</v>
+        <v>1.1221</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5985</v>
+        <v>1.3986</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4751</v>
+        <v>-0.2765</v>
       </c>
       <c r="G5" t="n">
         <v>2.0533</v>
@@ -844,13 +844,13 @@
         <v>0.9654</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2977</v>
+        <v>0.2965</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3032</v>
+        <v>0.1033</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0055</v>
+        <v>0.1932</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2277</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.66</v>
+        <v>0.7345</v>
       </c>
       <c r="E6" t="n">
         <v>0.4618</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1981</v>
+        <v>0.2726</v>
       </c>
       <c r="G6" t="n">
         <v>0.5239</v>
@@ -922,13 +922,13 @@
         <v>0.9654</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.7585</v>
       </c>
       <c r="T6" t="n">
         <v>0.3584</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3256</v>
+        <v>0.4001</v>
       </c>
       <c r="V6" t="n">
         <v>-1.5133</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. IYOHA OSARENKHOE</t>
+          <t>A. DIAZ CARBALLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.279</v>
+        <v>0.6097</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1387</v>
+        <v>-2.8649</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4177</v>
+        <v>3.4746</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2214</v>
+        <v>-1.2438</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9931</v>
+        <v>-2.2068</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2283</v>
+        <v>0.963</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-1.3943</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6481</v>
+        <v>-1.5164</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0407</v>
+        <v>0.1221</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.614</v>
+        <v>0.1505</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.345</v>
+        <v>-0.6904</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.269</v>
+        <v>0.8409</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7723</v>
+        <v>1.9308</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7723</v>
+        <v>2.8962</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7281</v>
+        <v>0.5792</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4688</v>
+        <v>0.1513</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2594</v>
+        <v>0.4279</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. DIAZ CARBALLO</t>
+          <t>D. IYOHA OSARENKHOE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1297</v>
+        <v>-0.0561</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.1821</v>
+        <v>-0.4489</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0524</v>
+        <v>0.3928</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2438</v>
+        <v>-1.2214</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.2068</v>
+        <v>-0.9931</v>
       </c>
       <c r="I8" t="n">
-        <v>0.963</v>
+        <v>-0.2283</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3943</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.5164</v>
+        <v>-0.6481</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1221</v>
+        <v>0.0407</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1505</v>
+        <v>-0.614</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6904</v>
+        <v>-0.345</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8409</v>
+        <v>-0.269</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9308</v>
+        <v>0.7723</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.8962</v>
+        <v>0.7723</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1601</v>
+        <v>0.393</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1659</v>
+        <v>0.1585</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0058</v>
+        <v>0.2345</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6018</v>
+        <v>-0.399</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4687</v>
+        <v>-1.3653</v>
       </c>
       <c r="F9" t="n">
-        <v>0.867</v>
+        <v>0.9663</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8689</v>
@@ -1156,13 +1156,13 @@
         <v>1.1585</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6453</v>
+        <v>0.8481</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4411</v>
+        <v>0.5445</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2042</v>
+        <v>0.3036</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5712</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0702</v>
+        <v>-0.7392</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2076</v>
+        <v>-0.0008</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8626</v>
+        <v>-0.7383999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2838</v>
@@ -1234,13 +1234,13 @@
         <v>0.9654</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5241</v>
+        <v>-0.1931</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3311</v>
+        <v>-0.1242</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.193</v>
+        <v>-0.0689</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2277</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3944</v>
+        <v>-3.2205</v>
       </c>
       <c r="E11" t="n">
         <v>-5.923</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5287</v>
+        <v>2.7025</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9041</v>
@@ -1312,13 +1312,13 @@
         <v>2.1239</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2152</v>
+        <v>-0.0414</v>
       </c>
       <c r="T11" t="n">
         <v>-0.1934</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0218</v>
+        <v>0.152</v>
       </c>
       <c r="V11" t="n">
         <v>1.4281</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3461</v>
+        <v>-3.2883</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.2975</v>
+        <v>-6.4632</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9514</v>
+        <v>3.1749</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2226</v>
@@ -1390,13 +1390,13 @@
         <v>3.2823</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2853</v>
+        <v>-0.2275</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0209</v>
+        <v>-0.1866</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2643</v>
+        <v>-0.0409</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3282</v>
@@ -1423,25 +1423,25 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.455199999999998</v>
+        <v>10.0072</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.1498</v>
+        <v>-10.5979</v>
       </c>
       <c r="F13" t="n">
         <v>20.6053</v>
       </c>
       <c r="G13" t="n">
-        <v>6.482900000000001</v>
+        <v>6.482900000000003</v>
       </c>
       <c r="H13" t="n">
         <v>1.034500000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>5.448300000000001</v>
+        <v>5.4483</v>
       </c>
       <c r="J13" t="n">
-        <v>4.319900000000001</v>
+        <v>4.319899999999999</v>
       </c>
       <c r="K13" t="n">
         <v>5.868</v>
@@ -1453,7 +1453,7 @@
         <v>2.163</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.833400000000001</v>
+        <v>-4.833399999999999</v>
       </c>
       <c r="O13" t="n">
         <v>6.996499999999999</v>
@@ -1468,13 +1468,13 @@
         <v>20.2732</v>
       </c>
       <c r="S13" t="n">
-        <v>2.482600000000001</v>
+        <v>3.0345</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1412</v>
+        <v>0.4106999999999998</v>
       </c>
       <c r="U13" t="n">
-        <v>2.6239</v>
+        <v>2.6237</v>
       </c>
       <c r="V13" t="n">
         <v>-1.4408</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.527</v>
+        <v>7.5089</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6057</v>
+        <v>4.2262</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9213</v>
+        <v>3.2827</v>
       </c>
       <c r="G14" t="n">
         <v>3.0953</v>
@@ -1546,13 +1546,13 @@
         <v>3.2823</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3406</v>
+        <v>-0.3587</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0486</v>
+        <v>-0.428</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.292</v>
+        <v>0.0694</v>
       </c>
       <c r="V14" t="n">
         <v>2.4554</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. VILLALBA BAULBYS</t>
+          <t>M. MIJE BENITEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7215</v>
+        <v>2.1471</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7903</v>
+        <v>0.6502</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9311</v>
+        <v>1.4968</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1287</v>
+        <v>2.7223</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1995</v>
+        <v>1.4066</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9292</v>
+        <v>1.3157</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2474</v>
+        <v>2.6405</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7522</v>
+        <v>2.0278</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4952</v>
+        <v>0.6127</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1187</v>
+        <v>0.0818</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5527</v>
+        <v>-0.6212</v>
       </c>
       <c r="O15" t="n">
-        <v>0.434</v>
+        <v>0.703</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3862</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3169</v>
+        <v>1.9308</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4343</v>
+        <v>-0.2896</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1302</v>
+        <v>-0.3451</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3041</v>
+        <v>0.0555</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.6565</v>
+        <v>0.2856</v>
       </c>
       <c r="X15" t="n">
         <v>-0.5712</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. MIJE BENITEZ</t>
+          <t>M. VILLALBA BAULBYS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3042</v>
+        <v>1.4527</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8571</v>
+        <v>-0.2439</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4471</v>
+        <v>1.6965</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7223</v>
+        <v>2.1287</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4066</v>
+        <v>1.1995</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3157</v>
+        <v>0.9292</v>
       </c>
       <c r="J16" t="n">
-        <v>2.6405</v>
+        <v>2.2474</v>
       </c>
       <c r="K16" t="n">
-        <v>2.0278</v>
+        <v>1.7522</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6127</v>
+        <v>0.4952</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0818</v>
+        <v>-0.1187</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6212</v>
+        <v>-0.5527</v>
       </c>
       <c r="O16" t="n">
-        <v>0.703</v>
+        <v>0.434</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.3862</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9308</v>
+        <v>2.3169</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1324</v>
+        <v>0.1655</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1383</v>
+        <v>0.096</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0058</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2856</v>
+        <v>-1.2277</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2856</v>
+        <v>-0.6565</v>
       </c>
       <c r="X16" t="n">
         <v>-0.5712</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GARCIA BORREGO</t>
+          <t>A. ANDRADE ROSSI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0951</v>
+        <v>-1.349</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.3387</v>
+        <v>-3.2661</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2436</v>
+        <v>1.9171</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.9882</v>
+        <v>-4.1434</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0409</v>
+        <v>-4.4825</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9473</v>
+        <v>0.3391</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9863</v>
+        <v>-3.9557</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2706</v>
+        <v>-3.9987</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2569</v>
+        <v>0.043</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0019</v>
+        <v>-0.1877</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3115</v>
+        <v>-0.4838</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3096</v>
+        <v>0.2961</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7377</v>
+        <v>1.5446</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R17" t="n">
-        <v>3.6685</v>
+        <v>2.51</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9543</v>
+        <v>-0.6344</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5784</v>
+        <v>-0.8004</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3759</v>
+        <v>0.166</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.7989</v>
+        <v>1.8842</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.4554</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.7989</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ANDRADE ROSSI</t>
+          <t>A. GARCIA BORREGO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8013</v>
+        <v>-2.0081</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.6798</v>
+        <v>-3.1661</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8785</v>
+        <v>1.158</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.1434</v>
+        <v>-1.9882</v>
       </c>
       <c r="H18" t="n">
-        <v>-4.4825</v>
+        <v>-1.0409</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3391</v>
+        <v>-0.9473</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.9557</v>
+        <v>-0.9863</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.9987</v>
+        <v>0.2706</v>
       </c>
       <c r="L18" t="n">
-        <v>0.043</v>
+        <v>-1.2569</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1877</v>
+        <v>-1.0019</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4838</v>
+        <v>-1.3115</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2961</v>
+        <v>0.3096</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5446</v>
+        <v>1.7377</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R18" t="n">
-        <v>2.51</v>
+        <v>3.6685</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0867</v>
+        <v>0.0413</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2141</v>
+        <v>-0.249</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1275</v>
+        <v>0.2903</v>
       </c>
       <c r="V18" t="n">
-        <v>1.8842</v>
+        <v>-1.7989</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4554</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5712</v>
+        <v>-1.7989</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5847</v>
+        <v>-2.1006</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7689</v>
+        <v>-2.4587</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1842</v>
+        <v>0.3581</v>
       </c>
       <c r="G19" t="n">
         <v>-3.2895</v>
@@ -1936,13 +1936,13 @@
         <v>0.9654</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5462</v>
+        <v>-0.0621</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4415</v>
+        <v>-0.1312</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1047</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>0.2856</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.3163</v>
+        <v>-3.8433</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.4931</v>
+        <v>-5.1829</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1768</v>
+        <v>1.3395</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7248</v>
@@ -2014,13 +2014,13 @@
         <v>2.1239</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2246</v>
+        <v>-0.7516</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9381</v>
+        <v>-0.6278</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2865</v>
+        <v>-0.1238</v>
       </c>
       <c r="V20" t="n">
         <v>0.3709</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-11.2107</v>
+        <v>-10.5735</v>
       </c>
       <c r="E21" t="n">
-        <v>-11.5778</v>
+        <v>-11.1641</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3671</v>
+        <v>0.5906</v>
       </c>
       <c r="G21" t="n">
         <v>-3.2831</v>
@@ -2092,13 +2092,13 @@
         <v>1.5446</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5407</v>
+        <v>0.0965</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.1383</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0112</v>
+        <v>0.2347</v>
       </c>
       <c r="V21" t="n">
         <v>-0.243</v>
@@ -2125,31 +2125,31 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.455400000000001</v>
+        <v>-8.765800000000002</v>
       </c>
       <c r="E22" t="n">
-        <v>-20.6052</v>
+        <v>-20.6054</v>
       </c>
       <c r="F22" t="n">
-        <v>11.1497</v>
+        <v>11.8393</v>
       </c>
       <c r="G22" t="n">
-        <v>-6.482699999999999</v>
+        <v>-6.482699999999998</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.034599999999998</v>
+        <v>-1.0346</v>
       </c>
       <c r="I22" t="n">
-        <v>-5.448200000000001</v>
+        <v>-5.4482</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.162900000000002</v>
+        <v>-2.1629</v>
       </c>
       <c r="K22" t="n">
         <v>4.833299999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>-6.9962</v>
+        <v>-6.996199999999999</v>
       </c>
       <c r="M22" t="n">
         <v>-4.32</v>
@@ -2170,13 +2170,13 @@
         <v>18.3424</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.4826</v>
+        <v>-1.7931</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.6239</v>
+        <v>-2.6238</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1413</v>
+        <v>0.8307</v>
       </c>
       <c r="V22" t="n">
         <v>1.4409</v>
